--- a/tests/fixtures/expected/veranstaltungen_tr.xlsx
+++ b/tests/fixtures/expected/veranstaltungen_tr.xlsx
@@ -556,7 +556,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2606WANFeierabendwanderung</t>
+          <t>26 Sonntagswanderung 0605 Feierabendwanderung</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2606MTBFeierabendrundeMTB</t>
+          <t>26 Mountainbike 0612 Feierabendrunde MTB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/tests/fixtures/expected/veranstaltungen_tr.xlsx
+++ b/tests/fixtures/expected/veranstaltungen_tr.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[dates]2026-06-05 18:00:00 bis 2026-06-05 23:59:59</t>
+          <t>[dates]2026-06-05 18:00:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[dates]2026-06-12 18:30:00 bis 2026-06-12 23:59:59</t>
+          <t>[dates]2026-06-12 18:30:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
